--- a/output7/【河洛文讀注音-閩拼調號】《禮記‧大學》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調號】《禮記‧大學》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F07F3B06-B2A1-4573-B9B1-8745787A928E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{393DA387-4584-4EBC-9FB2-9766D193B0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="1" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="718" activeTab="1" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="env" sheetId="8" r:id="rId1"/>
@@ -10123,7 +10123,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -10356,20 +10356,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="46" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="45" fillId="2" borderId="3" xfId="5" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="47" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="48" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyFill="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -31641,7 +31627,7 @@
       <c r="E159" s="67"/>
       <c r="F159" s="67"/>
       <c r="G159" s="67"/>
-      <c r="H159" s="78"/>
+      <c r="H159" s="67"/>
       <c r="I159" s="67"/>
       <c r="J159" s="67"/>
       <c r="K159" s="67"/>
@@ -31651,7 +31637,7 @@
       <c r="O159" s="67"/>
       <c r="P159" s="67"/>
       <c r="Q159" s="67"/>
-      <c r="R159" s="78"/>
+      <c r="R159" s="67"/>
       <c r="V159" s="36"/>
     </row>
     <row r="160" spans="2:22" s="6" customFormat="1" ht="36" customHeight="1">
@@ -31666,7 +31652,7 @@
       <c r="G160" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="H160" s="79" t="s">
+      <c r="H160" s="64" t="s">
         <v>1928</v>
       </c>
       <c r="I160" s="64" t="s">
@@ -31694,7 +31680,7 @@
       <c r="Q160" s="64" t="s">
         <v>336</v>
       </c>
-      <c r="R160" s="79" t="s">
+      <c r="R160" s="64" t="s">
         <v>379</v>
       </c>
       <c r="S160" s="19"/>
@@ -31717,7 +31703,7 @@
       <c r="G161" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="H161" s="77" t="s">
+      <c r="H161" s="68" t="s">
         <v>251</v>
       </c>
       <c r="I161" s="68" t="s">
@@ -31747,7 +31733,7 @@
       <c r="Q161" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="R161" s="77" t="s">
+      <c r="R161" s="68" t="s">
         <v>2011</v>
       </c>
       <c r="S161" s="21"/>
@@ -31765,7 +31751,7 @@
       <c r="G162" s="69" t="s">
         <v>2233</v>
       </c>
-      <c r="H162" s="80" t="s">
+      <c r="H162" s="69" t="s">
         <v>1928</v>
       </c>
       <c r="I162" s="69" t="s">
@@ -31793,7 +31779,7 @@
       <c r="Q162" s="69" t="s">
         <v>2213</v>
       </c>
-      <c r="R162" s="80" t="s">
+      <c r="R162" s="69" t="s">
         <v>2205</v>
       </c>
       <c r="S162" s="31"/>
@@ -31929,7 +31915,7 @@
       <c r="O167" s="67"/>
       <c r="P167" s="67"/>
       <c r="Q167" s="67"/>
-      <c r="R167" s="78"/>
+      <c r="R167" s="67"/>
     </row>
     <row r="168" spans="2:22" ht="44.25">
       <c r="B168" s="17"/>
@@ -31962,7 +31948,7 @@
       <c r="Q168" s="64" t="s">
         <v>1648</v>
       </c>
-      <c r="R168" s="79" t="s">
+      <c r="R168" s="64" t="s">
         <v>2967</v>
       </c>
     </row>
@@ -32014,7 +32000,7 @@
       <c r="Q169" s="68" t="s">
         <v>1527</v>
       </c>
-      <c r="R169" s="77" t="s">
+      <c r="R169" s="68" t="s">
         <v>2015</v>
       </c>
     </row>
@@ -32049,7 +32035,7 @@
       <c r="Q170" s="69" t="s">
         <v>2323</v>
       </c>
-      <c r="R170" s="80" t="s">
+      <c r="R170" s="69" t="s">
         <v>2968</v>
       </c>
     </row>
@@ -32974,7 +32960,7 @@
       <c r="L199" s="67"/>
       <c r="M199" s="67"/>
       <c r="N199" s="67"/>
-      <c r="O199" s="78"/>
+      <c r="O199" s="67"/>
       <c r="P199" s="67"/>
       <c r="Q199" s="67"/>
       <c r="R199" s="67"/>
@@ -33011,7 +32997,7 @@
       <c r="N200" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="O200" s="79" t="s">
+      <c r="O200" s="64" t="s">
         <v>54</v>
       </c>
       <c r="P200" s="64"/>
@@ -33057,7 +33043,7 @@
       <c r="N201" s="68" t="s">
         <v>93</v>
       </c>
-      <c r="O201" s="77" t="s">
+      <c r="O201" s="68" t="s">
         <v>34</v>
       </c>
       <c r="P201" s="68" t="s">
@@ -33102,7 +33088,7 @@
       <c r="N202" s="69" t="s">
         <v>2220</v>
       </c>
-      <c r="O202" s="80" t="s">
+      <c r="O202" s="69" t="s">
         <v>2341</v>
       </c>
       <c r="P202" s="69"/>
@@ -33272,7 +33258,7 @@
       <c r="L207" s="67"/>
       <c r="M207" s="67"/>
       <c r="N207" s="67"/>
-      <c r="O207" s="78"/>
+      <c r="O207" s="67"/>
       <c r="P207" s="67"/>
       <c r="Q207" s="67"/>
       <c r="R207" s="67"/>
@@ -33301,7 +33287,7 @@
       <c r="N208" s="64" t="s">
         <v>1165</v>
       </c>
-      <c r="O208" s="79" t="s">
+      <c r="O208" s="64" t="s">
         <v>2970</v>
       </c>
       <c r="P208" s="64"/>
@@ -33351,7 +33337,7 @@
       <c r="N209" s="68" t="s">
         <v>2030</v>
       </c>
-      <c r="O209" s="77" t="s">
+      <c r="O209" s="68" t="s">
         <v>2031</v>
       </c>
       <c r="P209" s="68" t="s">
@@ -33388,7 +33374,7 @@
       <c r="N210" s="69" t="s">
         <v>1344</v>
       </c>
-      <c r="O210" s="80" t="s">
+      <c r="O210" s="69" t="s">
         <v>2971</v>
       </c>
       <c r="P210" s="69"/>
@@ -34298,7 +34284,7 @@
       <c r="I235" s="67"/>
       <c r="J235" s="67"/>
       <c r="K235" s="67"/>
-      <c r="L235" s="78"/>
+      <c r="L235" s="67"/>
       <c r="M235" s="67"/>
       <c r="N235" s="67"/>
       <c r="O235" s="67"/>
@@ -34327,7 +34313,7 @@
       <c r="K236" s="64" t="s">
         <v>482</v>
       </c>
-      <c r="L236" s="79" t="s">
+      <c r="L236" s="64" t="s">
         <v>814</v>
       </c>
       <c r="M236" s="64" t="s">
@@ -34377,7 +34363,7 @@
       <c r="K237" s="68" t="s">
         <v>297</v>
       </c>
-      <c r="L237" s="77" t="s">
+      <c r="L237" s="68" t="s">
         <v>2044</v>
       </c>
       <c r="M237" s="68" t="s">
@@ -34420,7 +34406,7 @@
       <c r="K238" s="69" t="s">
         <v>2358</v>
       </c>
-      <c r="L238" s="80" t="s">
+      <c r="L238" s="69" t="s">
         <v>2972</v>
       </c>
       <c r="M238" s="69" t="s">
@@ -37403,7 +37389,7 @@
       <c r="H315" s="67"/>
       <c r="I315" s="67"/>
       <c r="J315" s="67"/>
-      <c r="K315" s="78"/>
+      <c r="K315" s="67"/>
       <c r="L315" s="67"/>
       <c r="M315" s="67"/>
       <c r="N315" s="67"/>
@@ -37432,7 +37418,7 @@
       <c r="J316" s="64" t="s">
         <v>1421</v>
       </c>
-      <c r="K316" s="79" t="s">
+      <c r="K316" s="64" t="s">
         <v>2974</v>
       </c>
       <c r="L316" s="64" t="s">
@@ -37480,7 +37466,7 @@
       <c r="J317" s="68" t="s">
         <v>1465</v>
       </c>
-      <c r="K317" s="77" t="s">
+      <c r="K317" s="68" t="s">
         <v>121</v>
       </c>
       <c r="L317" s="68" t="s">
@@ -37525,7 +37511,7 @@
       <c r="J318" s="69" t="s">
         <v>2208</v>
       </c>
-      <c r="K318" s="80" t="s">
+      <c r="K318" s="69" t="s">
         <v>2975</v>
       </c>
       <c r="L318" s="69" t="s">
@@ -37857,7 +37843,7 @@
       <c r="G327" s="67"/>
       <c r="H327" s="67"/>
       <c r="I327" s="67"/>
-      <c r="J327" s="78"/>
+      <c r="J327" s="67"/>
       <c r="K327" s="67"/>
       <c r="L327" s="67"/>
       <c r="M327" s="67"/>
@@ -37888,7 +37874,7 @@
       <c r="I328" s="64" t="s">
         <v>57</v>
       </c>
-      <c r="J328" s="79" t="s">
+      <c r="J328" s="64" t="s">
         <v>2977</v>
       </c>
       <c r="K328" s="64" t="s">
@@ -37936,7 +37922,7 @@
       <c r="I329" s="68" t="s">
         <v>292</v>
       </c>
-      <c r="J329" s="77" t="s">
+      <c r="J329" s="68" t="s">
         <v>2071</v>
       </c>
       <c r="K329" s="68" t="s">
@@ -37985,7 +37971,7 @@
       <c r="I330" s="69" t="s">
         <v>1320</v>
       </c>
-      <c r="J330" s="80" t="s">
+      <c r="J330" s="69" t="s">
         <v>2978</v>
       </c>
       <c r="K330" s="69" t="s">
@@ -38336,7 +38322,7 @@
       <c r="K339" s="67"/>
       <c r="L339" s="67"/>
       <c r="M339" s="67"/>
-      <c r="N339" s="78"/>
+      <c r="N339" s="67"/>
       <c r="O339" s="67"/>
       <c r="P339" s="67"/>
       <c r="Q339" s="67"/>
@@ -38371,7 +38357,7 @@
         <v>413</v>
       </c>
       <c r="M340" s="64"/>
-      <c r="N340" s="79" t="s">
+      <c r="N340" s="64" t="s">
         <v>2404</v>
       </c>
       <c r="O340" s="64"/>
@@ -38421,7 +38407,7 @@
       <c r="M341" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="N341" s="77" t="s">
+      <c r="N341" s="68" t="s">
         <v>2078</v>
       </c>
       <c r="O341" s="68" t="s">
@@ -38466,7 +38452,7 @@
         <v>2221</v>
       </c>
       <c r="M342" s="69"/>
-      <c r="N342" s="80" t="s">
+      <c r="N342" s="69" t="s">
         <v>2405</v>
       </c>
       <c r="O342" s="69"/>
@@ -38805,7 +38791,7 @@
       <c r="E351" s="67"/>
       <c r="F351" s="67"/>
       <c r="G351" s="67"/>
-      <c r="H351" s="78"/>
+      <c r="H351" s="67"/>
       <c r="I351" s="67"/>
       <c r="J351" s="67"/>
       <c r="K351" s="67"/>
@@ -38830,7 +38816,7 @@
       <c r="G352" s="64" t="s">
         <v>387</v>
       </c>
-      <c r="H352" s="79" t="s">
+      <c r="H352" s="64" t="s">
         <v>2979</v>
       </c>
       <c r="I352" s="64"/>
@@ -38880,7 +38866,7 @@
       <c r="G353" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="H353" s="77" t="s">
+      <c r="H353" s="68" t="s">
         <v>2081</v>
       </c>
       <c r="I353" s="68" t="s">
@@ -38927,7 +38913,7 @@
       <c r="G354" s="69" t="s">
         <v>2260</v>
       </c>
-      <c r="H354" s="80" t="s">
+      <c r="H354" s="69" t="s">
         <v>2980</v>
       </c>
       <c r="I354" s="69"/>
@@ -39895,7 +39881,7 @@
       <c r="D379" s="67"/>
       <c r="E379" s="67"/>
       <c r="F379" s="67"/>
-      <c r="G379" s="78"/>
+      <c r="G379" s="67"/>
       <c r="H379" s="67"/>
       <c r="I379" s="67"/>
       <c r="J379" s="67"/>
@@ -39916,7 +39902,7 @@
       <c r="F380" s="64" t="s">
         <v>1602</v>
       </c>
-      <c r="G380" s="79" t="s">
+      <c r="G380" s="64" t="s">
         <v>551</v>
       </c>
       <c r="H380" s="64" t="s">
@@ -39964,7 +39950,7 @@
       <c r="F381" s="68" t="s">
         <v>1471</v>
       </c>
-      <c r="G381" s="77" t="s">
+      <c r="G381" s="68" t="s">
         <v>2093</v>
       </c>
       <c r="H381" s="68" t="s">
@@ -40009,7 +39995,7 @@
       <c r="F382" s="69" t="s">
         <v>2311</v>
       </c>
-      <c r="G382" s="80" t="s">
+      <c r="G382" s="69" t="s">
         <v>551</v>
       </c>
       <c r="H382" s="69" t="s">
@@ -40054,7 +40040,7 @@
       <c r="J383" s="67"/>
       <c r="K383" s="67"/>
       <c r="L383" s="67"/>
-      <c r="M383" s="78"/>
+      <c r="M383" s="67"/>
       <c r="N383" s="67"/>
       <c r="O383" s="67"/>
       <c r="P383" s="67"/>
@@ -40083,7 +40069,7 @@
       <c r="L384" s="64" t="s">
         <v>387</v>
       </c>
-      <c r="M384" s="79" t="s">
+      <c r="M384" s="64" t="s">
         <v>2982</v>
       </c>
       <c r="N384" s="64"/>
@@ -40133,7 +40119,7 @@
       <c r="L385" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="M385" s="77" t="s">
+      <c r="M385" s="68" t="s">
         <v>2094</v>
       </c>
       <c r="N385" s="68" t="s">
@@ -40174,7 +40160,7 @@
       <c r="L386" s="69" t="s">
         <v>2260</v>
       </c>
-      <c r="M386" s="80" t="s">
+      <c r="M386" s="69" t="s">
         <v>2983</v>
       </c>
       <c r="N386" s="69"/>
@@ -40676,7 +40662,7 @@
       <c r="N399" s="67"/>
       <c r="O399" s="67"/>
       <c r="P399" s="67"/>
-      <c r="Q399" s="78"/>
+      <c r="Q399" s="67"/>
       <c r="R399" s="67"/>
     </row>
     <row r="400" spans="2:18" ht="44.25">
@@ -40717,7 +40703,7 @@
       <c r="P400" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="Q400" s="79" t="s">
+      <c r="Q400" s="64" t="s">
         <v>2407</v>
       </c>
       <c r="R400" s="64" t="s">
@@ -40769,7 +40755,7 @@
       <c r="P401" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="Q401" s="77" t="s">
+      <c r="Q401" s="68" t="s">
         <v>2096</v>
       </c>
       <c r="R401" s="68" t="s">
@@ -40814,7 +40800,7 @@
       <c r="P402" s="69" t="s">
         <v>2428</v>
       </c>
-      <c r="Q402" s="80" t="s">
+      <c r="Q402" s="69" t="s">
         <v>2408</v>
       </c>
       <c r="R402" s="69" t="s">
@@ -42655,7 +42641,7 @@
       <c r="J451" s="67"/>
       <c r="K451" s="67"/>
       <c r="L451" s="67"/>
-      <c r="M451" s="78"/>
+      <c r="M451" s="67"/>
       <c r="N451" s="67"/>
       <c r="O451" s="67"/>
       <c r="P451" s="67"/>
@@ -42684,7 +42670,7 @@
       <c r="L452" s="64" t="s">
         <v>1607</v>
       </c>
-      <c r="M452" s="79" t="s">
+      <c r="M452" s="64" t="s">
         <v>2984</v>
       </c>
       <c r="N452" s="64" t="s">
@@ -42734,7 +42720,7 @@
       <c r="L453" s="68" t="s">
         <v>1467</v>
       </c>
-      <c r="M453" s="77" t="s">
+      <c r="M453" s="68" t="s">
         <v>2110</v>
       </c>
       <c r="N453" s="68" t="s">
@@ -42775,7 +42761,7 @@
       <c r="L454" s="69" t="s">
         <v>2239</v>
       </c>
-      <c r="M454" s="80" t="s">
+      <c r="M454" s="69" t="s">
         <v>2985</v>
       </c>
       <c r="N454" s="69" t="s">
@@ -43438,7 +43424,7 @@
       <c r="L471" s="67"/>
       <c r="M471" s="67"/>
       <c r="N471" s="67"/>
-      <c r="O471" s="78"/>
+      <c r="O471" s="67"/>
       <c r="P471" s="67"/>
       <c r="Q471" s="67"/>
       <c r="R471" s="67"/>
@@ -43475,7 +43461,7 @@
       <c r="N472" s="64" t="s">
         <v>2206</v>
       </c>
-      <c r="O472" s="79" t="s">
+      <c r="O472" s="64" t="s">
         <v>2987</v>
       </c>
       <c r="P472" s="64" t="s">
@@ -43525,7 +43511,7 @@
       <c r="N473" s="68" t="s">
         <v>1945</v>
       </c>
-      <c r="O473" s="77" t="s">
+      <c r="O473" s="68" t="s">
         <v>2116</v>
       </c>
       <c r="P473" s="68" t="s">
@@ -43570,7 +43556,7 @@
       <c r="N474" s="69" t="s">
         <v>2207</v>
       </c>
-      <c r="O474" s="80" t="s">
+      <c r="O474" s="69" t="s">
         <v>2988</v>
       </c>
       <c r="P474" s="69" t="s">
@@ -45719,7 +45705,7 @@
       <c r="L531" s="67"/>
       <c r="M531" s="67"/>
       <c r="N531" s="67"/>
-      <c r="O531" s="78"/>
+      <c r="O531" s="67"/>
       <c r="P531" s="67"/>
       <c r="Q531" s="67"/>
       <c r="R531" s="67"/>
@@ -45756,7 +45742,7 @@
       <c r="N532" s="64" t="s">
         <v>387</v>
       </c>
-      <c r="O532" s="79" t="s">
+      <c r="O532" s="64" t="s">
         <v>539</v>
       </c>
       <c r="P532" s="64"/>
@@ -45806,7 +45792,7 @@
       <c r="N533" s="68" t="s">
         <v>168</v>
       </c>
-      <c r="O533" s="77" t="s">
+      <c r="O533" s="68" t="s">
         <v>81</v>
       </c>
       <c r="P533" s="68" t="s">
@@ -45851,7 +45837,7 @@
       <c r="N534" s="69" t="s">
         <v>2260</v>
       </c>
-      <c r="O534" s="80" t="s">
+      <c r="O534" s="69" t="s">
         <v>1892</v>
       </c>
       <c r="P534" s="69"/>
@@ -46034,7 +46020,7 @@
       <c r="I539" s="67"/>
       <c r="J539" s="67"/>
       <c r="K539" s="67"/>
-      <c r="L539" s="78"/>
+      <c r="L539" s="67"/>
       <c r="M539" s="67"/>
       <c r="N539" s="67"/>
       <c r="O539" s="67"/>
@@ -46065,7 +46051,7 @@
       <c r="K540" s="64" t="s">
         <v>2478</v>
       </c>
-      <c r="L540" s="79" t="s">
+      <c r="L540" s="64" t="s">
         <v>2990</v>
       </c>
       <c r="M540" s="64" t="s">
@@ -46115,7 +46101,7 @@
       <c r="K541" s="68" t="s">
         <v>2150</v>
       </c>
-      <c r="L541" s="77" t="s">
+      <c r="L541" s="68" t="s">
         <v>2151</v>
       </c>
       <c r="M541" s="68" t="s">
@@ -46160,7 +46146,7 @@
       <c r="K542" s="69" t="s">
         <v>1165</v>
       </c>
-      <c r="L542" s="80" t="s">
+      <c r="L542" s="69" t="s">
         <v>2991</v>
       </c>
       <c r="M542" s="69" t="s">
@@ -48364,7 +48350,7 @@
       <c r="J599" s="67"/>
       <c r="K599" s="67"/>
       <c r="L599" s="67"/>
-      <c r="M599" s="78"/>
+      <c r="M599" s="67"/>
       <c r="N599" s="67"/>
       <c r="O599" s="67"/>
       <c r="P599" s="67"/>
@@ -48397,7 +48383,7 @@
       <c r="L600" s="64" t="s">
         <v>448</v>
       </c>
-      <c r="M600" s="79" t="s">
+      <c r="M600" s="64" t="s">
         <v>2992</v>
       </c>
       <c r="N600" s="64"/>
@@ -48447,7 +48433,7 @@
       <c r="L601" s="68" t="s">
         <v>2178</v>
       </c>
-      <c r="M601" s="77" t="s">
+      <c r="M601" s="68" t="s">
         <v>2179</v>
       </c>
       <c r="N601" s="68" t="s">
@@ -48492,7 +48478,7 @@
       <c r="L602" s="69" t="s">
         <v>2347</v>
       </c>
-      <c r="M602" s="80" t="s">
+      <c r="M602" s="69" t="s">
         <v>2993</v>
       </c>
       <c r="N602" s="69"/>
@@ -48841,7 +48827,7 @@
       <c r="L611" s="67"/>
       <c r="M611" s="67"/>
       <c r="N611" s="67"/>
-      <c r="O611" s="78"/>
+      <c r="O611" s="67"/>
       <c r="P611" s="67"/>
       <c r="Q611" s="67"/>
       <c r="R611" s="67"/>
@@ -48878,7 +48864,7 @@
       <c r="N612" s="64" t="s">
         <v>421</v>
       </c>
-      <c r="O612" s="79" t="s">
+      <c r="O612" s="64" t="s">
         <v>1688</v>
       </c>
       <c r="P612" s="64" t="s">
@@ -48930,7 +48916,7 @@
       <c r="N613" s="68" t="s">
         <v>210</v>
       </c>
-      <c r="O613" s="77" t="s">
+      <c r="O613" s="68" t="s">
         <v>1592</v>
       </c>
       <c r="P613" s="68" t="s">
@@ -48975,7 +48961,7 @@
       <c r="N614" s="69" t="s">
         <v>2198</v>
       </c>
-      <c r="O614" s="80" t="s">
+      <c r="O614" s="69" t="s">
         <v>2514</v>
       </c>
       <c r="P614" s="69" t="s">
